--- a/March_Release_DBS/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,13 +466,13 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>17657</v>
+        <v>523158</v>
       </c>
       <c r="D2" t="str">
-        <v>WikiLTDPma</v>
+        <v>Jovany</v>
       </c>
       <c r="E2" t="str">
-        <v>2256</v>
+        <v>1161</v>
       </c>
       <c r="F2" t="str">
         <v>Collections</v>
@@ -484,7 +484,7 @@
         <v>12345321</v>
       </c>
       <c r="I2" t="str">
-        <v>BOOPS9614B</v>
+        <v>PANCA9614B</v>
       </c>
       <c r="J2" t="str">
         <v>hamad</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>9960072202</v>
+        <v>1921044473</v>
       </c>
       <c r="O2" t="str">
-        <v>hamad0679@yopmail.com</v>
+        <v>jovany@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
@@ -514,7 +514,7 @@
         <v>10-10-2032</v>
       </c>
       <c r="S2" t="str">
-        <v>Bulk upl$%56oad</v>
+        <v>Bulk upload</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_DBS/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>523158</v>
+        <v>748530</v>
       </c>
       <c r="D2" t="str">
-        <v>Jovany</v>
+        <v>D'angelo</v>
       </c>
       <c r="E2" t="str">
         <v>1161</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>1921044473</v>
+        <v>8205652416</v>
       </c>
       <c r="O2" t="str">
-        <v>jovany@yopmail.com</v>
+        <v>d'angelo@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
@@ -514,7 +514,7 @@
         <v>10-10-2032</v>
       </c>
       <c r="S2" t="str">
-        <v>Bulk upload</v>
+        <v>Bulk upl$%56oad</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_DBS/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,19 +466,19 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>258089</v>
+        <v>673472</v>
       </c>
       <c r="D2" t="str">
-        <v>Gilbert</v>
+        <v>Rudy</v>
       </c>
       <c r="E2" t="str">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="F2" t="str">
-        <v>Collection Staff Backend</v>
+        <v>Collections</v>
       </c>
       <c r="G2" t="str">
-        <v>Collection Backend Manager</v>
+        <v>Field Agents</v>
       </c>
       <c r="H2" t="str">
         <v>12345321</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>4696717327</v>
+        <v>2956746100</v>
       </c>
       <c r="O2" t="str">
-        <v>gilbert@yopmail.com</v>
+        <v>rudy@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>

--- a/March_Release_DBS/Cypress/fixtures/AgencyTemplate.xlsx
+++ b/March_Release_DBS/Cypress/fixtures/AgencyTemplate.xlsx
@@ -466,10 +466,10 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>673472</v>
+        <v>721366</v>
       </c>
       <c r="D2" t="str">
-        <v>Rudy</v>
+        <v>Jettie</v>
       </c>
       <c r="E2" t="str">
         <v>1161</v>
@@ -499,10 +499,10 @@
         <v>wiki field</v>
       </c>
       <c r="N2" t="str">
-        <v>2956746100</v>
+        <v>2175157559</v>
       </c>
       <c r="O2" t="str">
-        <v>rudy@yopmail.com</v>
+        <v>jettie@yopmail.com</v>
       </c>
       <c r="P2" t="str">
         <v>12-10-2022</v>
